--- a/backend/Final_Category.xlsx
+++ b/backend/Final_Category.xlsx
@@ -649,7 +649,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2362"/>
+  <dimension ref="A1:D2364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.86214285714286" bestFit="1" customWidth="1" style="20" min="1" max="1"/>
@@ -52614,6 +52614,50 @@
         </is>
       </c>
     </row>
+    <row r="2363">
+      <c r="A2363" t="inlineStr">
+        <is>
+          <t>upi-vivantapetroleum-paytmqr281005050101p30717s1oxug@paytm-pytm0123456-310863665271-upi</t>
+        </is>
+      </c>
+      <c r="B2363" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="C2363" t="inlineStr">
+        <is>
+          <t>aiyaz</t>
+        </is>
+      </c>
+      <c r="D2363" t="inlineStr">
+        <is>
+          <t>Important Expenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="2364">
+      <c r="A2364" t="inlineStr">
+        <is>
+          <t>debitcardissuancefee170223-mir2411077945410</t>
+        </is>
+      </c>
+      <c r="B2364" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="C2364" t="inlineStr">
+        <is>
+          <t>manish</t>
+        </is>
+      </c>
+      <c r="D2364" t="inlineStr">
+        <is>
+          <t>Important Expenses</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/backend/Final_Category.xlsx
+++ b/backend/Final_Category.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Workplace\Bizpedia\ca offline multiple clones\ca-offline-suite\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43C6DEA6-C210-45CE-8E25-D90BB949A99C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A469FA46-9B00-4819-A550-9CA84AE279C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9440" uniqueCount="2226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9440" uniqueCount="2228">
   <si>
     <t>Description</t>
   </si>
@@ -6698,6 +6698,12 @@
   </si>
   <si>
     <t>achc-oilandnaturalgas</t>
+  </si>
+  <si>
+    <t>Contra Credit</t>
+  </si>
+  <si>
+    <t>Contra Debit</t>
   </si>
 </sst>
 </file>
@@ -8370,7 +8376,7 @@
         <v>89</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>7</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8384,7 +8390,7 @@
         <v>89</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>7</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8398,7 +8404,7 @@
         <v>89</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>7</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8412,7 +8418,7 @@
         <v>89</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>7</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8426,7 +8432,7 @@
         <v>89</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>7</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8440,7 +8446,7 @@
         <v>89</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>7</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8454,7 +8460,7 @@
         <v>89</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>7</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8468,7 +8474,7 @@
         <v>89</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>7</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8482,7 +8488,7 @@
         <v>89</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>7</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8496,7 +8502,7 @@
         <v>89</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>7</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8510,7 +8516,7 @@
         <v>89</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>7</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8524,7 +8530,7 @@
         <v>89</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>7</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8538,7 +8544,7 @@
         <v>89</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>7</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8566,7 +8572,7 @@
         <v>104</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>10</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8580,7 +8586,7 @@
         <v>104</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>10</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8594,7 +8600,7 @@
         <v>104</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>10</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8608,7 +8614,7 @@
         <v>104</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>10</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8622,7 +8628,7 @@
         <v>104</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>10</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8636,7 +8642,7 @@
         <v>104</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>10</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8650,7 +8656,7 @@
         <v>104</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>10</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8664,7 +8670,7 @@
         <v>104</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>10</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8678,7 +8684,7 @@
         <v>104</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>10</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8692,7 +8698,7 @@
         <v>104</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>10</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8706,7 +8712,7 @@
         <v>104</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>10</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8720,7 +8726,7 @@
         <v>104</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>10</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8734,7 +8740,7 @@
         <v>104</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>10</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8748,7 +8754,7 @@
         <v>104</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>10</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8762,7 +8768,7 @@
         <v>104</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>10</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8776,7 +8782,7 @@
         <v>104</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>10</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8790,7 +8796,7 @@
         <v>104</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>10</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8804,7 +8810,7 @@
         <v>104</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>10</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8818,7 +8824,7 @@
         <v>104</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>10</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -8832,7 +8838,7 @@
         <v>104</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>10</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">

--- a/backend/Final_Category.xlsx
+++ b/backend/Final_Category.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2379"/>
+  <dimension ref="A1:E2381"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col width="28.81640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -55352,6 +55352,60 @@
         </is>
       </c>
     </row>
+    <row r="2380">
+      <c r="A2380" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B2380" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="C2380" t="inlineStr">
+        <is>
+          <t>raj</t>
+        </is>
+      </c>
+      <c r="D2380" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="E2380" t="inlineStr">
+        <is>
+          <t>non_default</t>
+        </is>
+      </c>
+    </row>
+    <row r="2381">
+      <c r="A2381" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B2381" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="C2381" t="inlineStr">
+        <is>
+          <t>raj2</t>
+        </is>
+      </c>
+      <c r="D2381" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="E2381" t="inlineStr">
+        <is>
+          <t>non_default</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E2374"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/backend/Final_Category.xlsx
+++ b/backend/Final_Category.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Workplace\Bizpedia\ca offline multiple clones\ca-offline-suite\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD8C92DE-BD3A-4930-8645-0AF8639D988F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCF785B1-1F9C-4F79-8622-0E1547D683E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9493" uniqueCount="2238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9509" uniqueCount="2240">
   <si>
     <t>Description</t>
   </si>
@@ -6737,6 +6737,12 @@
   </si>
   <si>
     <t>/jio/</t>
+  </si>
+  <si>
+    <t>navifinservlimited</t>
+  </si>
+  <si>
+    <t>angelone</t>
   </si>
 </sst>
 </file>
@@ -7247,7 +7253,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:E2373"/>
+  <dimension ref="A1:E2377"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28.81640625" bestFit="1" customWidth="1"/>
@@ -40484,6 +40490,62 @@
         <v>11</v>
       </c>
     </row>
+    <row r="2374" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2374" t="s">
+        <v>2238</v>
+      </c>
+      <c r="B2374" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2374" t="s">
+        <v>338</v>
+      </c>
+      <c r="D2374" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2375" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2375" t="s">
+        <v>2238</v>
+      </c>
+      <c r="B2375" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2375" t="s">
+        <v>337</v>
+      </c>
+      <c r="D2375" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2376" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2376" t="s">
+        <v>2239</v>
+      </c>
+      <c r="B2376" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2376" t="s">
+        <v>255</v>
+      </c>
+      <c r="D2376" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="2377" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2377" t="s">
+        <v>2239</v>
+      </c>
+      <c r="B2377" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2377" t="s">
+        <v>365</v>
+      </c>
+      <c r="D2377" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E2373" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
